--- a/artfynd/A 21382-2025 artfynd.xlsx
+++ b/artfynd/A 21382-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>62400378</v>
       </c>
       <c r="B2" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539727.0333438992</v>
+        <v>539727</v>
       </c>
       <c r="R2" t="n">
-        <v>6678920.410606387</v>
+        <v>6678920</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1950-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1950-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89198558</v>
+        <v>89198494</v>
       </c>
       <c r="B3" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,19 +797,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224363</v>
+        <v>224361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -841,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539520.1894333615</v>
+        <v>539520</v>
       </c>
       <c r="R3" t="n">
-        <v>6678868.014168301</v>
+        <v>6678868</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -874,19 +858,9 @@
           <t>2020-07-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89198494</v>
+        <v>89198558</v>
       </c>
       <c r="B4" t="n">
-        <v>95514</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,16 +909,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224361</v>
+        <v>224363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig lopplummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago subsp. selago</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -964,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539520.1894333615</v>
+        <v>539520</v>
       </c>
       <c r="R4" t="n">
-        <v>6678868.014168301</v>
+        <v>6678868</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -997,19 +966,9 @@
           <t>2020-07-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 21382-2025 artfynd.xlsx
+++ b/artfynd/A 21382-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Dalaflorans databas</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62400378</t>
         </is>
       </c>
     </row>
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89198494</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,8 +1018,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89198558</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>